--- a/Result/profitability/8917.xlsx
+++ b/Result/profitability/8917.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.545</v>
+        <v>0.5812499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>17.7875</v>
+        <v>17.9525</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.57</v>
+        <v>0.61875</v>
       </c>
       <c r="N3" t="n">
-        <v>18.405</v>
+        <v>19.0925</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>0.59875</v>
+        <v>0.63375</v>
       </c>
       <c r="N4" t="n">
-        <v>19.43875</v>
+        <v>19.8725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5975</v>
+        <v>0.6212500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.6925</v>
+        <v>19.7175</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5875</v>
+        <v>0.62375</v>
       </c>
       <c r="N6" t="n">
-        <v>19.095</v>
+        <v>19.50125</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61375</v>
+        <v>0.6512500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>20.30375</v>
+        <v>20.83875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6412500000000001</v>
+        <v>0.66625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.05375</v>
+        <v>22.4675</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.41</v>
       </c>
       <c r="M10" t="n">
-        <v>0.595</v>
+        <v>0.5950000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>21.35125</v>
@@ -1899,7 +1899,7 @@
         <v>0.57</v>
       </c>
       <c r="M12" t="n">
-        <v>0.58625</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>21.9125</v>
@@ -2026,7 +2026,7 @@
         <v>0.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0.62</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>22.83625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8917</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>749</v>
+      </c>
+      <c r="D75" t="n">
+        <v>594</v>
+      </c>
+      <c r="E75" t="n">
+        <v>156</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>126</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>161</v>
+      </c>
+      <c r="K75" t="n">
+        <v>134</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.12375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.309999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1893592677345537</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3015873015873014</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.009713453132588645</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
